--- a/SourceCode/EV_ERP/EV_ERP/wwwroot/templates/DNTT-template.xlsx
+++ b/SourceCode/EV_ERP/EV_ERP/wwwroot/templates/DNTT-template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Dev\EV_ERP_History\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Dev\EV_ERP\SourceCode\EV_ERP\EV_ERP\wwwroot\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20C98267-492D-4BB4-BE5F-B7D16CDDDF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA8312FE-8B1D-4747-93DA-8922DC8B9C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1253,113 +1253,113 @@
     <xf numFmtId="166" fontId="16" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="18" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="166" fontId="22" fillId="7" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="18" fillId="12" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="26" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="15" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="19" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="9" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="16" fillId="9" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="29" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="20" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="166" fontId="21" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="16" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="3" fontId="16" fillId="5" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="24" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="166" fontId="24" fillId="2" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="24" fillId="2" borderId="6" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="24" fillId="10" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="3" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="16" fillId="0" borderId="5" xfId="4" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="29" fillId="2" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="30" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="20" fillId="3" borderId="2" xfId="3" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="17" fillId="0" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="9" borderId="1" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="166" fontId="21" fillId="6" borderId="1" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="9" borderId="2" xfId="4" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="16" fillId="9" borderId="2" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="15" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="19" fillId="11" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="3" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="4" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="16" fillId="0" borderId="5" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="166" fontId="28" fillId="14" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="25" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="18" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="18" fillId="12" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="166" fontId="26" fillId="4" borderId="0" xfId="2" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="8">
@@ -1773,25 +1773,25 @@
       <c r="C1" s="1"/>
       <c r="E1" s="67"/>
       <c r="F1" s="14"/>
-      <c r="G1" s="130" t="s">
+      <c r="G1" s="141" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="130"/>
-      <c r="I1" s="130"/>
-      <c r="J1" s="130"/>
-      <c r="K1" s="130"/>
-      <c r="L1" s="130"/>
-      <c r="M1" s="130"/>
-      <c r="N1" s="130"/>
-      <c r="O1" s="130"/>
-      <c r="P1" s="130"/>
-      <c r="Q1" s="130"/>
-      <c r="R1" s="130"/>
-      <c r="S1" s="130"/>
-      <c r="T1" s="130"/>
-      <c r="U1" s="130"/>
-      <c r="V1" s="130"/>
-      <c r="W1" s="130"/>
+      <c r="H1" s="141"/>
+      <c r="I1" s="141"/>
+      <c r="J1" s="141"/>
+      <c r="K1" s="141"/>
+      <c r="L1" s="141"/>
+      <c r="M1" s="141"/>
+      <c r="N1" s="141"/>
+      <c r="O1" s="141"/>
+      <c r="P1" s="141"/>
+      <c r="Q1" s="141"/>
+      <c r="R1" s="141"/>
+      <c r="S1" s="141"/>
+      <c r="T1" s="141"/>
+      <c r="U1" s="141"/>
+      <c r="V1" s="141"/>
+      <c r="W1" s="141"/>
     </row>
     <row r="2" spans="1:23" ht="63" customHeight="1">
       <c r="A2" s="1"/>
@@ -1799,25 +1799,25 @@
       <c r="C2" s="1"/>
       <c r="E2" s="13"/>
       <c r="F2" s="12"/>
-      <c r="G2" s="131" t="s">
+      <c r="G2" s="142" t="s">
         <v>48</v>
       </c>
-      <c r="H2" s="131"/>
-      <c r="I2" s="131"/>
-      <c r="J2" s="131"/>
-      <c r="K2" s="131"/>
-      <c r="L2" s="131"/>
-      <c r="M2" s="131"/>
-      <c r="N2" s="131"/>
-      <c r="O2" s="131"/>
-      <c r="P2" s="131"/>
-      <c r="Q2" s="131"/>
-      <c r="R2" s="131"/>
-      <c r="S2" s="131"/>
-      <c r="T2" s="131"/>
-      <c r="U2" s="131"/>
-      <c r="V2" s="131"/>
-      <c r="W2" s="131"/>
+      <c r="H2" s="142"/>
+      <c r="I2" s="142"/>
+      <c r="J2" s="142"/>
+      <c r="K2" s="142"/>
+      <c r="L2" s="142"/>
+      <c r="M2" s="142"/>
+      <c r="N2" s="142"/>
+      <c r="O2" s="142"/>
+      <c r="P2" s="142"/>
+      <c r="Q2" s="142"/>
+      <c r="R2" s="142"/>
+      <c r="S2" s="142"/>
+      <c r="T2" s="142"/>
+      <c r="U2" s="142"/>
+      <c r="V2" s="142"/>
+      <c r="W2" s="142"/>
     </row>
     <row r="3" spans="1:23" ht="63" customHeight="1">
       <c r="A3" s="1"/>
@@ -1825,52 +1825,52 @@
       <c r="C3" s="1"/>
       <c r="E3" s="13"/>
       <c r="F3" s="12"/>
-      <c r="G3" s="131" t="s">
+      <c r="G3" s="142" t="s">
         <v>1</v>
       </c>
-      <c r="H3" s="131"/>
-      <c r="I3" s="131"/>
-      <c r="J3" s="131"/>
-      <c r="K3" s="131"/>
-      <c r="L3" s="131"/>
-      <c r="M3" s="131"/>
-      <c r="N3" s="131"/>
-      <c r="O3" s="131"/>
-      <c r="P3" s="131"/>
-      <c r="Q3" s="131"/>
-      <c r="R3" s="131"/>
-      <c r="S3" s="131"/>
-      <c r="T3" s="131"/>
-      <c r="U3" s="131"/>
-      <c r="V3" s="131"/>
-      <c r="W3" s="131"/>
+      <c r="H3" s="142"/>
+      <c r="I3" s="142"/>
+      <c r="J3" s="142"/>
+      <c r="K3" s="142"/>
+      <c r="L3" s="142"/>
+      <c r="M3" s="142"/>
+      <c r="N3" s="142"/>
+      <c r="O3" s="142"/>
+      <c r="P3" s="142"/>
+      <c r="Q3" s="142"/>
+      <c r="R3" s="142"/>
+      <c r="S3" s="142"/>
+      <c r="T3" s="142"/>
+      <c r="U3" s="142"/>
+      <c r="V3" s="142"/>
+      <c r="W3" s="142"/>
     </row>
     <row r="4" spans="1:23" ht="72" customHeight="1">
-      <c r="A4" s="132" t="s">
+      <c r="A4" s="143" t="s">
         <v>37</v>
       </c>
-      <c r="B4" s="132"/>
-      <c r="C4" s="132"/>
-      <c r="D4" s="132"/>
-      <c r="E4" s="132"/>
-      <c r="F4" s="132"/>
-      <c r="G4" s="132"/>
-      <c r="H4" s="132"/>
-      <c r="I4" s="132"/>
-      <c r="J4" s="132"/>
-      <c r="K4" s="132"/>
-      <c r="L4" s="132"/>
-      <c r="M4" s="132"/>
-      <c r="N4" s="132"/>
-      <c r="O4" s="132"/>
-      <c r="P4" s="132"/>
-      <c r="Q4" s="132"/>
-      <c r="R4" s="132"/>
-      <c r="S4" s="132"/>
-      <c r="T4" s="132"/>
-      <c r="U4" s="132"/>
-      <c r="V4" s="132"/>
-      <c r="W4" s="132"/>
+      <c r="B4" s="143"/>
+      <c r="C4" s="143"/>
+      <c r="D4" s="143"/>
+      <c r="E4" s="143"/>
+      <c r="F4" s="143"/>
+      <c r="G4" s="143"/>
+      <c r="H4" s="143"/>
+      <c r="I4" s="143"/>
+      <c r="J4" s="143"/>
+      <c r="K4" s="143"/>
+      <c r="L4" s="143"/>
+      <c r="M4" s="143"/>
+      <c r="N4" s="143"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="143"/>
+      <c r="R4" s="143"/>
+      <c r="S4" s="143"/>
+      <c r="T4" s="143"/>
+      <c r="U4" s="143"/>
+      <c r="V4" s="143"/>
+      <c r="W4" s="143"/>
     </row>
     <row r="5" spans="1:23" s="4" customFormat="1" ht="51" customHeight="1">
       <c r="A5" s="15" t="s">
@@ -1880,21 +1880,19 @@
       <c r="C5" s="15"/>
       <c r="D5" s="15"/>
       <c r="E5" s="82"/>
-      <c r="F5" s="135" t="s">
+      <c r="F5" s="146" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="135"/>
-      <c r="H5" s="135"/>
-      <c r="I5" s="134">
-        <v>123456</v>
-      </c>
-      <c r="J5" s="134"/>
-      <c r="K5" s="133" t="s">
+      <c r="G5" s="146"/>
+      <c r="H5" s="146"/>
+      <c r="I5" s="145"/>
+      <c r="J5" s="145"/>
+      <c r="K5" s="144" t="s">
         <v>38</v>
       </c>
-      <c r="L5" s="133"/>
-      <c r="M5" s="133"/>
-      <c r="N5" s="133"/>
+      <c r="L5" s="144"/>
+      <c r="M5" s="144"/>
+      <c r="N5" s="144"/>
       <c r="O5" s="48"/>
       <c r="P5" s="82"/>
       <c r="Q5" s="18"/>
@@ -2036,13 +2034,13 @@
         <f>+#REF!</f>
         <v>#REF!</v>
       </c>
-      <c r="D10" s="136" t="s">
+      <c r="D10" s="139" t="s">
         <v>43</v>
       </c>
-      <c r="E10" s="136"/>
-      <c r="F10" s="136"/>
-      <c r="G10" s="137"/>
-      <c r="H10" s="137"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="140"/>
+      <c r="H10" s="140"/>
       <c r="I10" s="89"/>
       <c r="J10" s="89"/>
       <c r="K10" s="89"/>
@@ -2207,16 +2205,16 @@
     </row>
     <row r="13" spans="1:23" s="1" customFormat="1" ht="63" customHeight="1">
       <c r="A13" s="50"/>
-      <c r="B13" s="151" t="s">
+      <c r="B13" s="149" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="152"/>
-      <c r="D13" s="153"/>
-      <c r="E13" s="124">
+      <c r="C13" s="150"/>
+      <c r="D13" s="151"/>
+      <c r="E13" s="152">
         <f>SUMPRODUCT(E12:E12,F12:F12)</f>
         <v>150000</v>
       </c>
-      <c r="F13" s="124"/>
+      <c r="F13" s="152"/>
       <c r="G13" s="68">
         <f>SUMPRODUCT(E12:E12,F12:F12,G12:G12)</f>
         <v>12000</v>
@@ -2226,15 +2224,15 @@
         <v>162000</v>
       </c>
       <c r="I13" s="52"/>
-      <c r="J13" s="138" t="s">
+      <c r="J13" s="153" t="s">
         <v>26</v>
       </c>
-      <c r="K13" s="138"/>
-      <c r="L13" s="124">
+      <c r="K13" s="153"/>
+      <c r="L13" s="152">
         <f>SUMPRODUCT(L8:L12,M8:M12)</f>
         <v>93075</v>
       </c>
-      <c r="M13" s="124"/>
+      <c r="M13" s="152"/>
       <c r="N13" s="68">
         <f>SUMPRODUCT(L8:L12,M8:M12,N8:N12)</f>
         <v>7446</v>
@@ -2267,13 +2265,13 @@
     <row r="14" spans="1:23" ht="50.4" customHeight="1">
       <c r="A14" s="53"/>
       <c r="B14" s="53"/>
-      <c r="C14" s="125"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="127">
+      <c r="C14" s="155"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="154">
         <f>SUMIF(N12:N12,"0",H12:H12)</f>
         <v>0</v>
       </c>
-      <c r="F14" s="127"/>
+      <c r="F14" s="154"/>
       <c r="G14" s="98" t="s">
         <v>28</v>
       </c>
@@ -2282,15 +2280,15 @@
         <v>#REF!</v>
       </c>
       <c r="I14" s="101"/>
-      <c r="J14" s="154" t="s">
+      <c r="J14" s="157" t="s">
         <v>47</v>
       </c>
-      <c r="K14" s="154"/>
-      <c r="L14" s="154"/>
-      <c r="M14" s="155" t="s">
+      <c r="K14" s="157"/>
+      <c r="L14" s="157"/>
+      <c r="M14" s="158" t="s">
         <v>30</v>
       </c>
-      <c r="N14" s="155"/>
+      <c r="N14" s="158"/>
       <c r="O14" s="113" t="e">
         <f>O13+Q13</f>
         <v>#REF!</v>
@@ -2298,10 +2296,10 @@
       <c r="P14" s="112" t="s">
         <v>24</v>
       </c>
-      <c r="Q14" s="156" t="s">
+      <c r="Q14" s="132" t="s">
         <v>41</v>
       </c>
-      <c r="R14" s="156"/>
+      <c r="R14" s="132"/>
       <c r="S14" s="111"/>
       <c r="T14" s="112" t="s">
         <v>24</v>
@@ -2319,21 +2317,21 @@
       <c r="G15" s="55"/>
       <c r="H15" s="56"/>
       <c r="I15" s="101"/>
-      <c r="J15" s="154"/>
-      <c r="K15" s="154"/>
-      <c r="L15" s="154"/>
-      <c r="M15" s="123" t="s">
+      <c r="J15" s="157"/>
+      <c r="K15" s="157"/>
+      <c r="L15" s="157"/>
+      <c r="M15" s="133" t="s">
         <v>39</v>
       </c>
-      <c r="N15" s="123"/>
+      <c r="N15" s="133"/>
       <c r="O15" s="96"/>
       <c r="P15" s="97" t="s">
         <v>24</v>
       </c>
-      <c r="Q15" s="157" t="s">
+      <c r="Q15" s="134" t="s">
         <v>46</v>
       </c>
-      <c r="R15" s="157"/>
+      <c r="R15" s="134"/>
       <c r="S15" s="105"/>
       <c r="T15" s="97" t="s">
         <v>24</v>
@@ -2354,18 +2352,18 @@
       <c r="J16" s="107"/>
       <c r="K16" s="108"/>
       <c r="L16" s="109"/>
-      <c r="M16" s="128" t="s">
+      <c r="M16" s="147" t="s">
         <v>56</v>
       </c>
-      <c r="N16" s="129"/>
+      <c r="N16" s="148"/>
       <c r="O16" s="121"/>
       <c r="P16" s="122" t="s">
         <v>24</v>
       </c>
-      <c r="Q16" s="142" t="s">
+      <c r="Q16" s="137" t="s">
         <v>53</v>
       </c>
-      <c r="R16" s="142"/>
+      <c r="R16" s="137"/>
       <c r="S16" s="113" t="e">
         <f>T13-O14</f>
         <v>#REF!</v>
@@ -2376,8 +2374,8 @@
       <c r="U16" s="120" t="s">
         <v>54</v>
       </c>
-      <c r="V16" s="143"/>
-      <c r="W16" s="143"/>
+      <c r="V16" s="138"/>
+      <c r="W16" s="138"/>
     </row>
     <row r="17" spans="1:28" ht="50.4" customHeight="1">
       <c r="A17" s="53"/>
@@ -2405,39 +2403,39 @@
       <c r="W17" s="92"/>
     </row>
     <row r="18" spans="1:28" ht="51" customHeight="1">
-      <c r="A18" s="144" t="s">
+      <c r="A18" s="123" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="144"/>
-      <c r="C18" s="144"/>
-      <c r="D18" s="144" t="s">
+      <c r="B18" s="123"/>
+      <c r="C18" s="123"/>
+      <c r="D18" s="123" t="s">
         <v>6</v>
       </c>
-      <c r="E18" s="144"/>
-      <c r="F18" s="144"/>
-      <c r="G18" s="145" t="s">
+      <c r="E18" s="123"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="145"/>
+      <c r="H18" s="124"/>
       <c r="I18" s="62"/>
-      <c r="J18" s="144" t="s">
+      <c r="J18" s="123" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="144"/>
-      <c r="L18" s="144"/>
-      <c r="M18" s="144"/>
-      <c r="N18" s="144"/>
+      <c r="K18" s="123"/>
+      <c r="L18" s="123"/>
+      <c r="M18" s="123"/>
+      <c r="N18" s="123"/>
       <c r="O18" s="58"/>
       <c r="P18" s="66"/>
       <c r="Q18" s="78"/>
       <c r="R18" s="78"/>
       <c r="S18" s="78"/>
-      <c r="T18" s="146" t="s">
+      <c r="T18" s="136" t="s">
         <v>52</v>
       </c>
-      <c r="U18" s="146"/>
-      <c r="V18" s="146"/>
-      <c r="W18" s="146"/>
+      <c r="U18" s="136"/>
+      <c r="V18" s="136"/>
+      <c r="W18" s="136"/>
     </row>
     <row r="19" spans="1:28" ht="48.75" customHeight="1">
       <c r="A19" s="57"/>
@@ -2459,10 +2457,10 @@
       <c r="Q19" s="79"/>
       <c r="R19" s="79"/>
       <c r="S19" s="79"/>
-      <c r="T19" s="146"/>
-      <c r="U19" s="146"/>
-      <c r="V19" s="146"/>
-      <c r="W19" s="146"/>
+      <c r="T19" s="136"/>
+      <c r="U19" s="136"/>
+      <c r="V19" s="136"/>
+      <c r="W19" s="136"/>
     </row>
     <row r="20" spans="1:28" ht="58.2" customHeight="1">
       <c r="A20" s="57"/>
@@ -2484,14 +2482,14 @@
       <c r="Q20" s="79"/>
       <c r="R20" s="79"/>
       <c r="S20" s="79"/>
-      <c r="T20" s="146"/>
-      <c r="U20" s="146"/>
-      <c r="V20" s="146"/>
-      <c r="W20" s="146"/>
-      <c r="Y20" s="158"/>
-      <c r="Z20" s="158"/>
-      <c r="AA20" s="158"/>
-      <c r="AB20" s="158"/>
+      <c r="T20" s="136"/>
+      <c r="U20" s="136"/>
+      <c r="V20" s="136"/>
+      <c r="W20" s="136"/>
+      <c r="Y20" s="135"/>
+      <c r="Z20" s="135"/>
+      <c r="AA20" s="135"/>
+      <c r="AB20" s="135"/>
     </row>
     <row r="21" spans="1:28" ht="48.75" customHeight="1">
       <c r="A21" s="57"/>
@@ -2513,71 +2511,71 @@
       <c r="Q21" s="79"/>
       <c r="R21" s="79"/>
       <c r="S21" s="79"/>
-      <c r="T21" s="146"/>
-      <c r="U21" s="146"/>
-      <c r="V21" s="146"/>
-      <c r="W21" s="146"/>
-      <c r="Y21" s="158"/>
-      <c r="Z21" s="158"/>
-      <c r="AA21" s="158"/>
-      <c r="AB21" s="158"/>
+      <c r="T21" s="136"/>
+      <c r="U21" s="136"/>
+      <c r="V21" s="136"/>
+      <c r="W21" s="136"/>
+      <c r="Y21" s="135"/>
+      <c r="Z21" s="135"/>
+      <c r="AA21" s="135"/>
+      <c r="AB21" s="135"/>
     </row>
     <row r="22" spans="1:28" ht="51.6" customHeight="1">
-      <c r="A22" s="150" t="e">
+      <c r="A22" s="128" t="e">
         <f>C6</f>
         <v>#REF!</v>
       </c>
-      <c r="B22" s="150"/>
-      <c r="C22" s="150"/>
-      <c r="D22" s="147"/>
-      <c r="E22" s="147"/>
-      <c r="F22" s="147"/>
-      <c r="G22" s="149" t="s">
+      <c r="B22" s="128"/>
+      <c r="C22" s="128"/>
+      <c r="D22" s="129"/>
+      <c r="E22" s="129"/>
+      <c r="F22" s="129"/>
+      <c r="G22" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="H22" s="149"/>
+      <c r="H22" s="130"/>
       <c r="I22" s="16"/>
-      <c r="J22" s="148"/>
-      <c r="K22" s="148"/>
-      <c r="L22" s="148"/>
-      <c r="M22" s="148"/>
-      <c r="N22" s="148"/>
+      <c r="J22" s="131"/>
+      <c r="K22" s="131"/>
+      <c r="L22" s="131"/>
+      <c r="M22" s="131"/>
+      <c r="N22" s="131"/>
       <c r="O22" s="16"/>
       <c r="P22" s="26"/>
       <c r="Q22" s="18"/>
-      <c r="T22" s="146"/>
-      <c r="U22" s="146"/>
-      <c r="V22" s="146"/>
-      <c r="W22" s="146"/>
-      <c r="Y22" s="158"/>
-      <c r="Z22" s="158"/>
-      <c r="AA22" s="158"/>
-      <c r="AB22" s="158"/>
+      <c r="T22" s="136"/>
+      <c r="U22" s="136"/>
+      <c r="V22" s="136"/>
+      <c r="W22" s="136"/>
+      <c r="Y22" s="135"/>
+      <c r="Z22" s="135"/>
+      <c r="AA22" s="135"/>
+      <c r="AB22" s="135"/>
     </row>
     <row r="23" spans="1:28" ht="85.2" customHeight="1">
-      <c r="A23" s="139"/>
-      <c r="B23" s="139"/>
-      <c r="C23" s="139"/>
-      <c r="D23" s="140"/>
-      <c r="E23" s="140"/>
-      <c r="F23" s="140"/>
-      <c r="G23" s="141"/>
-      <c r="H23" s="141"/>
+      <c r="A23" s="125"/>
+      <c r="B23" s="125"/>
+      <c r="C23" s="125"/>
+      <c r="D23" s="126"/>
+      <c r="E23" s="126"/>
+      <c r="F23" s="126"/>
+      <c r="G23" s="127"/>
+      <c r="H23" s="127"/>
       <c r="I23" s="28"/>
-      <c r="J23" s="140"/>
-      <c r="K23" s="140"/>
-      <c r="L23" s="140"/>
-      <c r="M23" s="140"/>
-      <c r="N23" s="140"/>
+      <c r="J23" s="126"/>
+      <c r="K23" s="126"/>
+      <c r="L23" s="126"/>
+      <c r="M23" s="126"/>
+      <c r="N23" s="126"/>
       <c r="O23" s="42"/>
       <c r="P23" s="28"/>
       <c r="Q23" s="18"/>
       <c r="R23" s="18"/>
       <c r="S23" s="18"/>
-      <c r="Y23" s="158"/>
-      <c r="Z23" s="158"/>
-      <c r="AA23" s="158"/>
-      <c r="AB23" s="158"/>
+      <c r="Y23" s="135"/>
+      <c r="Z23" s="135"/>
+      <c r="AA23" s="135"/>
+      <c r="AB23" s="135"/>
     </row>
     <row r="24" spans="1:28" ht="118.95" customHeight="1">
       <c r="A24" s="31"/>
@@ -2599,10 +2597,10 @@
       <c r="Q24" s="18"/>
       <c r="R24" s="18"/>
       <c r="S24" s="18"/>
-      <c r="Y24" s="158"/>
-      <c r="Z24" s="158"/>
-      <c r="AA24" s="158"/>
-      <c r="AB24" s="158"/>
+      <c r="Y24" s="135"/>
+      <c r="Z24" s="135"/>
+      <c r="AA24" s="135"/>
+      <c r="AB24" s="135"/>
     </row>
     <row r="25" spans="1:28" ht="63" customHeight="1">
       <c r="A25" s="32"/>
@@ -2829,6 +2827,31 @@
     </row>
   </sheetData>
   <mergeCells count="37">
+    <mergeCell ref="B13:D13"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="J13:K13"/>
+    <mergeCell ref="L13:M13"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="C14:D14"/>
+    <mergeCell ref="J14:L15"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="D10:F10"/>
+    <mergeCell ref="G10:H10"/>
+    <mergeCell ref="G1:W1"/>
+    <mergeCell ref="G2:W2"/>
+    <mergeCell ref="G3:W3"/>
+    <mergeCell ref="A4:W4"/>
+    <mergeCell ref="K5:N5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="F5:H5"/>
+    <mergeCell ref="Q14:R14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="Q15:R15"/>
+    <mergeCell ref="Y20:AB24"/>
+    <mergeCell ref="T18:W22"/>
+    <mergeCell ref="Q16:R16"/>
+    <mergeCell ref="V16:W16"/>
+    <mergeCell ref="M16:N16"/>
     <mergeCell ref="A18:C18"/>
     <mergeCell ref="D18:F18"/>
     <mergeCell ref="G18:H18"/>
@@ -2841,31 +2864,6 @@
     <mergeCell ref="D22:F22"/>
     <mergeCell ref="G22:H22"/>
     <mergeCell ref="J22:N22"/>
-    <mergeCell ref="Q14:R14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="Q15:R15"/>
-    <mergeCell ref="Y20:AB24"/>
-    <mergeCell ref="T18:W22"/>
-    <mergeCell ref="Q16:R16"/>
-    <mergeCell ref="V16:W16"/>
-    <mergeCell ref="D10:F10"/>
-    <mergeCell ref="G10:H10"/>
-    <mergeCell ref="G1:W1"/>
-    <mergeCell ref="G2:W2"/>
-    <mergeCell ref="G3:W3"/>
-    <mergeCell ref="A4:W4"/>
-    <mergeCell ref="K5:N5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="F5:H5"/>
-    <mergeCell ref="M16:N16"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="E13:F13"/>
-    <mergeCell ref="J13:K13"/>
-    <mergeCell ref="L13:M13"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="J14:L15"/>
-    <mergeCell ref="M14:N14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="21" fitToHeight="0" orientation="landscape" r:id="rId1"/>
